--- a/inventario.xlsx
+++ b/inventario.xlsx
@@ -10,19 +10,19 @@
   <definedNames>
     <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Container!$A$1:$C$116</definedName>
     <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">Magazzino!$A$1:$C$2</definedName>
-    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">Giochi!$A$1:$B$34</definedName>
+    <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">Giochi!$A$1:$B$70</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="qEYNwdNBGzdwUA72Jvltkr3F6gfOqOHPj3LGNcyX8i8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="CsLWlqX/pahDiYQ44L2+QQ624J6bWn+cE7GYdtkwkCU="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="376" uniqueCount="255">
   <si>
     <t>Descrizione</t>
   </si>
@@ -31,6 +31,21 @@
   </si>
   <si>
     <t>Ripiano</t>
+  </si>
+  <si>
+    <t>Addobbi natalizi</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>Arco</t>
+  </si>
+  <si>
+    <t>Bacinelle bolle</t>
+  </si>
+  <si>
+    <t>G</t>
   </si>
   <si>
     <t>Bacinelle grandi</t>
@@ -42,322 +57,100 @@
     <t>Bacinelle piccole</t>
   </si>
   <si>
-    <t>Secchielli</t>
+    <t>Bandierine</t>
   </si>
   <si>
-    <t>Scotch</t>
+    <t>F</t>
+  </si>
+  <si>
+    <t>Barattoli di latta</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>Bastoni</t>
+  </si>
+  <si>
+    <t>L</t>
+  </si>
+  <si>
+    <t>Bende</t>
+  </si>
+  <si>
+    <t>Bersaglio</t>
+  </si>
+  <si>
+    <t>Birilli</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>Bocce</t>
+  </si>
+  <si>
+    <t>Bocce quadre</t>
+  </si>
+  <si>
+    <t>Boccioni</t>
+  </si>
+  <si>
+    <t>Campanello x quiz</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>Canestri di plastica</t>
+  </si>
+  <si>
+    <t>Canestro di riserva</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>Canne da pesca</t>
+  </si>
+  <si>
+    <t>Cannoni ad Acqua</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>Carte Piccolo Principe</t>
   </si>
   <si>
     <t>Cartelloni</t>
   </si>
   <si>
-    <t>Pennarelli</t>
+    <t>Caselle gioco dell'oca</t>
+  </si>
+  <si>
+    <t>Cassette ruote</t>
+  </si>
+  <si>
+    <t>Catena/Lucchetti/Chiavi</t>
+  </si>
+  <si>
+    <t>Cerbottane</t>
+  </si>
+  <si>
+    <t>Ciabattoni</t>
+  </si>
+  <si>
+    <t>Cinesini arancioni/viola</t>
+  </si>
+  <si>
+    <t>Circo</t>
   </si>
   <si>
     <t>Colla vinilica</t>
   </si>
   <si>
-    <t>Bende</t>
-  </si>
-  <si>
-    <t>Roverino</t>
-  </si>
-  <si>
-    <t>Viti/Bulloni</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>Birilli</t>
-  </si>
-  <si>
-    <t>Bocce</t>
-  </si>
-  <si>
-    <t>Carte Piccolo Principe</t>
-  </si>
-  <si>
-    <t>Scalpi</t>
-  </si>
-  <si>
-    <t>Ovetti Kinder</t>
-  </si>
-  <si>
-    <t>Palline da calcetto</t>
-  </si>
-  <si>
-    <t>Palline da ping-pong</t>
-  </si>
-  <si>
-    <t>Racchette da ping-pong</t>
-  </si>
-  <si>
-    <t>Reti da ping-pong</t>
-  </si>
-  <si>
-    <t>Rullini</t>
-  </si>
-  <si>
-    <t>Mollette</t>
-  </si>
-  <si>
-    <t>Caselle gioco dell'oca</t>
-  </si>
-  <si>
-    <t>Circo</t>
-  </si>
-  <si>
-    <t>Palline biliardo</t>
-  </si>
-  <si>
-    <t>Corde</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>Coppe</t>
-  </si>
-  <si>
-    <t>Palline colorate</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>Coriandoli</t>
-  </si>
-  <si>
-    <t>Ruote/Picchetti</t>
-  </si>
-  <si>
-    <t>Cannoni ad Acqua</t>
-  </si>
-  <si>
-    <t>Pistole ad acqua</t>
-  </si>
-  <si>
-    <t>Strisce biancorosse</t>
-  </si>
-  <si>
     <t>Colori acrilici</t>
-  </si>
-  <si>
-    <t>Pesci</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>Rotoli di carta</t>
-  </si>
-  <si>
-    <t>Fresbee</t>
-  </si>
-  <si>
-    <t>Barattoli di latta</t>
-  </si>
-  <si>
-    <t>Setacci</t>
-  </si>
-  <si>
-    <t>Gavettoni</t>
-  </si>
-  <si>
-    <t>Spugne</t>
-  </si>
-  <si>
-    <t>Scatoloni</t>
-  </si>
-  <si>
-    <t>Corde campo</t>
-  </si>
-  <si>
-    <t>F</t>
-  </si>
-  <si>
-    <t>Ombreggiante</t>
-  </si>
-  <si>
-    <t>Tappi di sughero</t>
-  </si>
-  <si>
-    <t>Bocce quadre</t>
-  </si>
-  <si>
-    <t>Cinesini arancioni/viola</t>
-  </si>
-  <si>
-    <t>Dadi di legno</t>
-  </si>
-  <si>
-    <t>Domino stoffe</t>
-  </si>
-  <si>
-    <t>Catena/Lucchetti/Chiavi</t>
-  </si>
-  <si>
-    <t>Fischietti ultimo giorno</t>
-  </si>
-  <si>
-    <t>Gioco NOI</t>
-  </si>
-  <si>
-    <t>Picchetti</t>
-  </si>
-  <si>
-    <t>Racchettoni</t>
-  </si>
-  <si>
-    <t>Sacchi iuta</t>
-  </si>
-  <si>
-    <t>Bandierine</t>
-  </si>
-  <si>
-    <t>Palline di scotch</t>
-  </si>
-  <si>
-    <t>Cerbottane</t>
-  </si>
-  <si>
-    <t>Bacinelle bolle</t>
-  </si>
-  <si>
-    <t>G</t>
-  </si>
-  <si>
-    <t>Boccioni</t>
-  </si>
-  <si>
-    <t>Cassette ruote</t>
-  </si>
-  <si>
-    <t>Picchetti militari</t>
-  </si>
-  <si>
-    <t>Gonfiabili</t>
-  </si>
-  <si>
-    <t>Pompe gonfiabili</t>
-  </si>
-  <si>
-    <t>Scatola creatività</t>
-  </si>
-  <si>
-    <t>Palette</t>
-  </si>
-  <si>
-    <t>Piscina</t>
-  </si>
-  <si>
-    <t>Rete pallavolo</t>
-  </si>
-  <si>
-    <t>Reti laterali</t>
-  </si>
-  <si>
-    <t>Teli</t>
-  </si>
-  <si>
-    <t>Golf</t>
-  </si>
-  <si>
-    <t>H</t>
-  </si>
-  <si>
-    <t>Racchette tennis</t>
-  </si>
-  <si>
-    <t>Racchette volano</t>
-  </si>
-  <si>
-    <t>Tappetini</t>
-  </si>
-  <si>
-    <t>Volani</t>
-  </si>
-  <si>
-    <t>Palline da tennis</t>
-  </si>
-  <si>
-    <t>Molle trampolino</t>
-  </si>
-  <si>
-    <t>Scatola posate</t>
-  </si>
-  <si>
-    <t>Tappeto elastico</t>
-  </si>
-  <si>
-    <t>Trampolino pad</t>
-  </si>
-  <si>
-    <t>Materassini</t>
-  </si>
-  <si>
-    <t>Campanello x quiz</t>
-  </si>
-  <si>
-    <t>Canestri di plastica</t>
-  </si>
-  <si>
-    <t>Grondaia schiaccia noci</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Teli di bambù </t>
-  </si>
-  <si>
-    <t>Lance romane</t>
-  </si>
-  <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>Palloni di riserva</t>
-  </si>
-  <si>
-    <t>Canestro di riserva</t>
-  </si>
-  <si>
-    <t>Scudi romani</t>
-  </si>
-  <si>
-    <t>Porta da calcio</t>
-  </si>
-  <si>
-    <t>Rete da calcio con punti</t>
-  </si>
-  <si>
-    <t>Rete volano</t>
-  </si>
-  <si>
-    <t>Reti da calcio</t>
-  </si>
-  <si>
-    <t>Freccette</t>
-  </si>
-  <si>
-    <t>J</t>
-  </si>
-  <si>
-    <t>Arco</t>
-  </si>
-  <si>
-    <t>Bersaglio</t>
-  </si>
-  <si>
-    <t>Frecce</t>
-  </si>
-  <si>
-    <t>Mega cartelloni</t>
-  </si>
-  <si>
-    <t>Addobbi natalizi</t>
-  </si>
-  <si>
-    <t>Croquet</t>
   </si>
   <si>
     <t>Coni</t>
@@ -366,43 +159,100 @@
     <t>K</t>
   </si>
   <si>
-    <t>Hula hoop</t>
+    <t>Coppe</t>
   </si>
   <si>
-    <t>Bastoni</t>
+    <t>C</t>
   </si>
   <si>
-    <t>L</t>
+    <t>Corde</t>
   </si>
   <si>
-    <t>Canne da pesca</t>
+    <t>Corde campo</t>
+  </si>
+  <si>
+    <t>Coriandoli</t>
+  </si>
+  <si>
+    <t>Croquet</t>
+  </si>
+  <si>
+    <t>Dadi di legno</t>
+  </si>
+  <si>
+    <t>Dado di spugna</t>
+  </si>
+  <si>
+    <t>M</t>
+  </si>
+  <si>
+    <t>Domino stoffe</t>
+  </si>
+  <si>
+    <t>Fischietti ultimo giorno</t>
+  </si>
+  <si>
+    <t>Frecce</t>
+  </si>
+  <si>
+    <t>Freccette</t>
+  </si>
+  <si>
+    <t>Fresbee</t>
+  </si>
+  <si>
+    <t>Gavettoni</t>
   </si>
   <si>
     <t>Giavellotti</t>
   </si>
   <si>
-    <t>Retini</t>
+    <t>Gioco NOI</t>
   </si>
   <si>
-    <t>Sci legno</t>
+    <t>Golf</t>
   </si>
   <si>
-    <t>Ciabattoni</t>
+    <t>Gonfiabili</t>
+  </si>
+  <si>
+    <t>Grondaia schiaccia noci</t>
+  </si>
+  <si>
+    <t>Hula hoop</t>
+  </si>
+  <si>
+    <t>Lance romane</t>
+  </si>
+  <si>
+    <t>Materassini</t>
+  </si>
+  <si>
+    <t>Mega cartelloni</t>
+  </si>
+  <si>
+    <t>Molle trampolino</t>
+  </si>
+  <si>
+    <t>Mollette</t>
+  </si>
+  <si>
+    <t>Ombreggiante</t>
+  </si>
+  <si>
+    <t>Ovetti Kinder</t>
+  </si>
+  <si>
+    <t>Palette</t>
   </si>
   <si>
     <t>Palla da basket</t>
   </si>
   <si>
-    <t>M</t>
+    <t>Palla da calcio</t>
   </si>
   <si>
     <t>Palla da pallavolo</t>
-  </si>
-  <si>
-    <t>Palla da calcio</t>
-  </si>
-  <si>
-    <t>Dado di spugna</t>
   </si>
   <si>
     <t>Palla da rugby</t>
@@ -412,6 +262,156 @@
   </si>
   <si>
     <t>Palla morbida</t>
+  </si>
+  <si>
+    <t>Palline biliardo</t>
+  </si>
+  <si>
+    <t>Palline colorate</t>
+  </si>
+  <si>
+    <t>Palline da calcetto</t>
+  </si>
+  <si>
+    <t>Palline da ping-pong</t>
+  </si>
+  <si>
+    <t>Palline da tennis</t>
+  </si>
+  <si>
+    <t>Palline di scotch</t>
+  </si>
+  <si>
+    <t>Palloni di riserva</t>
+  </si>
+  <si>
+    <t>Pennarelli</t>
+  </si>
+  <si>
+    <t>Pesci</t>
+  </si>
+  <si>
+    <t>Picchetti</t>
+  </si>
+  <si>
+    <t>Picchetti militari</t>
+  </si>
+  <si>
+    <t>Piscina</t>
+  </si>
+  <si>
+    <t>Pistole ad acqua</t>
+  </si>
+  <si>
+    <t>Pompe gonfiabili</t>
+  </si>
+  <si>
+    <t>Porta da calcio</t>
+  </si>
+  <si>
+    <t>Racchette da ping-pong</t>
+  </si>
+  <si>
+    <t>Racchette tennis</t>
+  </si>
+  <si>
+    <t>Racchette volano</t>
+  </si>
+  <si>
+    <t>Racchettoni</t>
+  </si>
+  <si>
+    <t>Rete da calcio con punti</t>
+  </si>
+  <si>
+    <t>Rete pallavolo</t>
+  </si>
+  <si>
+    <t>Rete volano</t>
+  </si>
+  <si>
+    <t>Reti da calcio</t>
+  </si>
+  <si>
+    <t>Reti da ping-pong</t>
+  </si>
+  <si>
+    <t>Reti laterali</t>
+  </si>
+  <si>
+    <t>Retini</t>
+  </si>
+  <si>
+    <t>Rotoli di carta</t>
+  </si>
+  <si>
+    <t>Roverino</t>
+  </si>
+  <si>
+    <t>Rullini</t>
+  </si>
+  <si>
+    <t>Ruote/Picchetti</t>
+  </si>
+  <si>
+    <t>Sacchi iuta</t>
+  </si>
+  <si>
+    <t>Scalpi</t>
+  </si>
+  <si>
+    <t>Scatola creatività</t>
+  </si>
+  <si>
+    <t>Scatola posate</t>
+  </si>
+  <si>
+    <t>Scatoloni</t>
+  </si>
+  <si>
+    <t>Sci legno</t>
+  </si>
+  <si>
+    <t>Scotch</t>
+  </si>
+  <si>
+    <t>Scudi romani</t>
+  </si>
+  <si>
+    <t>Secchielli</t>
+  </si>
+  <si>
+    <t>Setacci</t>
+  </si>
+  <si>
+    <t>Spugne</t>
+  </si>
+  <si>
+    <t>Strisce biancorosse</t>
+  </si>
+  <si>
+    <t>Tappetini</t>
+  </si>
+  <si>
+    <t>Tappeto elastico</t>
+  </si>
+  <si>
+    <t>Tappi di sughero</t>
+  </si>
+  <si>
+    <t>Teli</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Teli di bambù </t>
+  </si>
+  <si>
+    <t>Trampolino pad</t>
+  </si>
+  <si>
+    <t>Viti/Bulloni</t>
+  </si>
+  <si>
+    <t>Volani</t>
   </si>
   <si>
     <t>Materiali</t>
@@ -590,6 +590,204 @@
   <si>
     <t>Prede e predatori</t>
   </si>
+  <si>
+    <t>Acchiappasogni</t>
+  </si>
+  <si>
+    <t>Lana;Cartone;Forbici;Scotch</t>
+  </si>
+  <si>
+    <t>Il sogno a catena</t>
+  </si>
+  <si>
+    <t>Tessere</t>
+  </si>
+  <si>
+    <t>Riflesso</t>
+  </si>
+  <si>
+    <t>Specchi</t>
+  </si>
+  <si>
+    <t>Molto onore ci darai</t>
+  </si>
+  <si>
+    <t>Stoffe;Vestiti;Gioielli</t>
+  </si>
+  <si>
+    <t>Farò di te un uomo</t>
+  </si>
+  <si>
+    <t>Corde;Panche;Sedie;Arco;Frecce;Bersaglio</t>
+  </si>
+  <si>
+    <t>Per le mi batterò</t>
+  </si>
+  <si>
+    <t>Bende;Oggetti schifosi</t>
+  </si>
+  <si>
+    <t>Ecco la lezione</t>
+  </si>
+  <si>
+    <t>Canne bambù</t>
+  </si>
+  <si>
+    <t>Mushu</t>
+  </si>
+  <si>
+    <t>Teli;Scalpi</t>
+  </si>
+  <si>
+    <t>Generale Shan</t>
+  </si>
+  <si>
+    <t>Corde;Palline colorate;Bacinelle;Fazzoletto</t>
+  </si>
+  <si>
+    <t>Guerrieri vs Unni</t>
+  </si>
+  <si>
+    <t>Aiutiamo Nani</t>
+  </si>
+  <si>
+    <t>Scatola posate;Spugne;Mollette;Corde;Panni;Pasta;Scope;Palette;Palline di scotch;Cestini</t>
+  </si>
+  <si>
+    <t>Esperimento 626</t>
+  </si>
+  <si>
+    <t>Bustina di tè vuota;Accendino;Piatto</t>
+  </si>
+  <si>
+    <t>L&amp;S</t>
+  </si>
+  <si>
+    <t>Occhiali da sole</t>
+  </si>
+  <si>
+    <t>Lili &amp; Stitches</t>
+  </si>
+  <si>
+    <t>Sedie</t>
+  </si>
+  <si>
+    <t>Antidoto</t>
+  </si>
+  <si>
+    <t>Carta igienica; Pistole ad acqua</t>
+  </si>
+  <si>
+    <t>Folle folla</t>
+  </si>
+  <si>
+    <t>Bottiglia d'acqua</t>
+  </si>
+  <si>
+    <t>99 scimmie</t>
+  </si>
+  <si>
+    <t>Gavettoni;Corde</t>
+  </si>
+  <si>
+    <t>L'imperatore</t>
+  </si>
+  <si>
+    <t>Spugne;Pistole ad acqua</t>
+  </si>
+  <si>
+    <t>Egocentrismo</t>
+  </si>
+  <si>
+    <t>Sedie;Gavettoni</t>
+  </si>
+  <si>
+    <t>Uvetta</t>
+  </si>
+  <si>
+    <t>Let's groove</t>
+  </si>
+  <si>
+    <t>Sedia;Cassa;Piscina</t>
+  </si>
+  <si>
+    <t>Camminata</t>
+  </si>
+  <si>
+    <t>Non si tocca!</t>
+  </si>
+  <si>
+    <t>Palloncini;Scatola;Spiedini</t>
+  </si>
+  <si>
+    <t>Cheddar</t>
+  </si>
+  <si>
+    <t>Post it</t>
+  </si>
+  <si>
+    <t>Arrampicata</t>
+  </si>
+  <si>
+    <t>Bastoni;Coni;Pallina da tennis;Sedie;Corde</t>
+  </si>
+  <si>
+    <t>Broccoletti</t>
+  </si>
+  <si>
+    <t>Palline colorate;Palla morbida;Bastoni</t>
+  </si>
+  <si>
+    <t>Acqua in bocca</t>
+  </si>
+  <si>
+    <t>Acqua;Bottiglia;Bicchieri</t>
+  </si>
+  <si>
+    <t>Palla retino con gavettoni</t>
+  </si>
+  <si>
+    <t>Retini;Gavettoni</t>
+  </si>
+  <si>
+    <t>Il cuore di te fiti</t>
+  </si>
+  <si>
+    <t>Mappa</t>
+  </si>
+  <si>
+    <t>La danza di Maui</t>
+  </si>
+  <si>
+    <t>La barca di Vaiana</t>
+  </si>
+  <si>
+    <t>I pesci di Hei Hei</t>
+  </si>
+  <si>
+    <t>Cartoncini;Fogli a forma di pesce</t>
+  </si>
+  <si>
+    <t>Il tesoro di Tomatoa</t>
+  </si>
+  <si>
+    <t>Corde;Ovetti Kinder</t>
+  </si>
+  <si>
+    <t>Maremoto</t>
+  </si>
+  <si>
+    <t>Barche</t>
+  </si>
+  <si>
+    <t>Carta;Colla;Forbici;Piscina;Acqua;Cerbottane</t>
+  </si>
+  <si>
+    <t>Onde</t>
+  </si>
+  <si>
+    <t>Tappetini;Corde</t>
+  </si>
 </sst>
 </file>
 
@@ -627,13 +825,13 @@
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
@@ -893,803 +1091,769 @@
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1">
       <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="C3" s="4"/>
     </row>
     <row r="4" ht="15.75" customHeight="1">
       <c r="A4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2">
+      <c r="B4" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="4">
         <v>1.0</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
-      <c r="A5" s="3" t="s">
-        <v>7</v>
+      <c r="A5" s="1" t="s">
+        <v>8</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="C5" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="6" ht="15.75" customHeight="1">
+      <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="7" ht="15.75" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="8" ht="15.75" customHeight="1">
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C8" s="4">
         <v>2.0</v>
-      </c>
-    </row>
-    <row r="6" ht="15.75" customHeight="1">
-      <c r="A6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="7" ht="15.75" customHeight="1">
-      <c r="A7" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="2">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>4</v>
-      </c>
-      <c r="C8" s="4">
-        <v>3.0</v>
       </c>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C9" s="4">
-        <v>4.0</v>
-      </c>
+        <v>15</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C9" s="4"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C10" s="2">
-        <v>5.0</v>
+        <v>17</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="3">
+        <v>4.0</v>
       </c>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="1" t="s">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="4">
-        <v>1.0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C11" s="4"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="2">
+        <v>19</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C12" s="4">
         <v>1.0</v>
       </c>
     </row>
     <row r="13" ht="15.75" customHeight="1">
       <c r="A13" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="2">
+        <v>21</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C13" s="4">
         <v>1.0</v>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1">
       <c r="A14" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C14" s="2">
+        <v>22</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C14" s="4">
         <v>2.0</v>
       </c>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="3" t="s">
-        <v>18</v>
+      <c r="A15" s="1" t="s">
+        <v>23</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C15" s="4">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1">
       <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C16" s="2">
-        <v>3.0</v>
+        <v>24</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C16" s="4">
+        <v>4.0</v>
       </c>
     </row>
     <row r="17" ht="15.75" customHeight="1">
       <c r="A17" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C17" s="2">
-        <v>3.0</v>
+        <v>26</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C17" s="4">
+        <v>4.0</v>
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C18" s="2">
-        <v>3.0</v>
-      </c>
+      <c r="A18" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C18" s="4"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="3" t="s">
-        <v>22</v>
+      <c r="A19" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C19" s="4">
-        <v>3.0</v>
-      </c>
+        <v>16</v>
+      </c>
+      <c r="C19" s="4"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="4">
+      <c r="A20" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1">
       <c r="A21" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C21" s="2">
-        <v>3.0</v>
+        <v>32</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C22" s="4">
-        <v>3.0</v>
+      <c r="A22" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C22" s="3">
+        <v>2.0</v>
       </c>
     </row>
     <row r="23" ht="15.75" customHeight="1">
       <c r="A23" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C23" s="2">
+        <v>34</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C23" s="4">
         <v>4.0</v>
       </c>
     </row>
     <row r="24" ht="15.75" customHeight="1">
       <c r="A24" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C24" s="2">
-        <v>4.0</v>
+        <v>35</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C24" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="25" ht="15.75" customHeight="1">
       <c r="A25" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="C25" s="2">
+        <v>36</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C25" s="4">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" s="3">
         <v>4.0</v>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C26" s="2">
-        <v>1.0</v>
-      </c>
-    </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="C27" s="4">
-        <v>2.0</v>
-      </c>
+      <c r="A27" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="4"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
       <c r="A28" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C28" s="2">
+        <v>39</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C28" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="4">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="3">
+        <v>3.0</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C31" s="4">
+        <v>4.0</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C32" s="4"/>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="3">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" s="4">
         <v>1.0</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C29" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C30" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C31" s="4">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C32" s="4">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C33" s="4">
-        <v>4.0</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C34" s="2">
-        <v>4.0</v>
       </c>
     </row>
     <row r="35" ht="15.75" customHeight="1">
       <c r="A35" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>41</v>
+        <v>12</v>
       </c>
       <c r="C35" s="4">
         <v>1.0</v>
       </c>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C36" s="2">
-        <v>1.0</v>
+      <c r="A36" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="3">
+        <v>2.0</v>
       </c>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C37" s="4">
-        <v>2.0</v>
-      </c>
+      <c r="A37" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C37" s="4"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C38" s="2">
+        <v>51</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="4">
         <v>2.0</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
       <c r="A39" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C39" s="2">
-        <v>2.0</v>
+        <v>52</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C39" s="3">
+        <v>1.0</v>
       </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
       <c r="A40" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="2">
-        <v>3.0</v>
+        <v>54</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
       <c r="A41" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="C41" s="2">
+        <v>55</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="4">
         <v>3.0</v>
       </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3" t="s">
-        <v>48</v>
+      <c r="A42" s="1" t="s">
+        <v>56</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="C42" s="4">
-        <v>4.0</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="C42" s="4"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
       <c r="A43" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C43" s="2">
-        <v>1.0</v>
-      </c>
+        <v>57</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="C43" s="4"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
       <c r="A44" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C44" s="2">
-        <v>1.0</v>
+        <v>58</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="3">
+        <v>2.0</v>
       </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
       <c r="A45" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C45" s="2">
-        <v>1.0</v>
+        <v>59</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="4">
+        <v>3.0</v>
       </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
       <c r="A46" s="1" t="s">
-        <v>53</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C46" s="2">
-        <v>2.0</v>
-      </c>
+        <v>60</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C46" s="4"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
       <c r="A47" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="B47" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C47" s="2">
-        <v>2.0</v>
+        <v>61</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" s="4">
+        <v>3.0</v>
       </c>
     </row>
     <row r="48" ht="15.75" customHeight="1">
       <c r="A48" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B48" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C48" s="2">
-        <v>2.0</v>
+        <v>62</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C48" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="49" ht="15.75" customHeight="1">
       <c r="A49" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B49" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C49" s="2">
+        <v>63</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="4">
         <v>2.0</v>
       </c>
     </row>
     <row r="50" ht="15.75" customHeight="1">
       <c r="A50" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="B50" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C50" s="2">
-        <v>3.0</v>
+        <v>64</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C50" s="4">
+        <v>4.0</v>
       </c>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="B51" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C51" s="2">
-        <v>3.0</v>
-      </c>
+      <c r="A51" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="B51" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C51" s="4"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
       <c r="A52" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C52" s="2">
-        <v>3.0</v>
-      </c>
+        <v>66</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C52" s="4"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
       <c r="A53" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="B53" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C53" s="2">
+        <v>67</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53" s="4">
         <v>3.0</v>
       </c>
     </row>
     <row r="54" ht="15.75" customHeight="1">
       <c r="A54" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="B54" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C54" s="2">
-        <v>3.0</v>
-      </c>
+        <v>68</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C54" s="4"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
       <c r="A55" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C55" s="2">
-        <v>3.0</v>
+        <v>69</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C55" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C56" s="4">
+      <c r="A56" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B56" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C56" s="3">
         <v>3.0</v>
       </c>
     </row>
     <row r="57" ht="15.75" customHeight="1">
       <c r="A57" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B57" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C57" s="2">
-        <v>4.0</v>
+        <v>71</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C57" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3" t="s">
-        <v>65</v>
+      <c r="A58" s="1" t="s">
+        <v>72</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="C58" s="4">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B59" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C59" s="2">
-        <v>1.0</v>
+      <c r="A59" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C59" s="4">
+        <v>2.0</v>
       </c>
     </row>
     <row r="60" ht="15.75" customHeight="1">
       <c r="A60" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B60" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C60" s="2">
-        <v>1.0</v>
-      </c>
+        <v>73</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C60" s="4"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="B61" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C61" s="2">
-        <v>1.0</v>
+      <c r="A61" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C61" s="3">
+        <v>4.0</v>
       </c>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B62" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C62" s="2">
-        <v>1.0</v>
+      <c r="A62" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C62" s="3">
+        <v>2.0</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B63" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C63" s="2">
-        <v>2.0</v>
+      <c r="A63" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C63" s="3">
+        <v>3.0</v>
       </c>
     </row>
     <row r="64" ht="15.75" customHeight="1">
       <c r="A64" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B64" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C64" s="2">
-        <v>2.0</v>
+        <v>77</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C64" s="3">
+        <v>1.0</v>
       </c>
     </row>
     <row r="65" ht="15.75" customHeight="1">
       <c r="A65" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B65" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C65" s="2">
-        <v>2.0</v>
+        <v>78</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C65" s="3">
+        <v>1.0</v>
       </c>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B66" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C66" s="2">
-        <v>2.0</v>
+      <c r="A66" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="C66" s="3">
+        <v>1.0</v>
       </c>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C67" s="2">
-        <v>3.0</v>
+      <c r="A67" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C67" s="4">
+        <v>4.0</v>
       </c>
     </row>
     <row r="68" ht="15.75" customHeight="1">
       <c r="A68" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B68" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C68" s="2">
-        <v>3.0</v>
+        <v>81</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C68" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="69" ht="15.75" customHeight="1">
       <c r="A69" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="2" t="s">
-        <v>67</v>
+        <v>82</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="C69" s="4">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3" t="s">
-        <v>78</v>
+      <c r="A70" s="1" t="s">
+        <v>83</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>67</v>
+        <v>20</v>
       </c>
       <c r="C70" s="4">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B71" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C71" s="2">
+      <c r="A71" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="B71" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C71" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="72" ht="15.75" customHeight="1">
       <c r="A72" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B72" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C72" s="2">
-        <v>1.0</v>
+        <v>85</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C72" s="4">
+        <v>4.0</v>
       </c>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C73" s="2">
-        <v>1.0</v>
-      </c>
+      <c r="A73" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="B73" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C73" s="4"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
       <c r="A74" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>80</v>
+        <v>87</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="C74" s="4">
         <v>3.0</v>
@@ -1697,413 +1861,447 @@
     </row>
     <row r="75" ht="15.75" customHeight="1">
       <c r="A75" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="B75" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C75" s="2">
+        <v>88</v>
+      </c>
+      <c r="B75" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C75" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3" t="s">
-        <v>85</v>
+      <c r="A76" s="1" t="s">
+        <v>89</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>80</v>
+        <v>12</v>
       </c>
       <c r="C76" s="4">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="77" ht="15.75" customHeight="1">
       <c r="A77" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="B77" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C77" s="2">
-        <v>2.0</v>
+        <v>90</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C77" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="B78" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C78" s="2">
-        <v>2.0</v>
+      <c r="A78" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C78" s="4">
+        <v>3.0</v>
       </c>
     </row>
     <row r="79" ht="15.75" customHeight="1">
       <c r="A79" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C79" s="2">
-        <v>2.0</v>
+        <v>92</v>
+      </c>
+      <c r="B79" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C79" s="3">
+        <v>3.0</v>
       </c>
     </row>
     <row r="80" ht="15.75" customHeight="1">
       <c r="A80" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C80" s="2">
+        <v>93</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="4">
         <v>2.0</v>
       </c>
     </row>
     <row r="81" ht="15.75" customHeight="1">
       <c r="A81" s="1" t="s">
-        <v>90</v>
-      </c>
-      <c r="B81" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C81" s="2">
+        <v>94</v>
+      </c>
+      <c r="B81" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C81" s="4"/>
+    </row>
+    <row r="82" ht="15.75" customHeight="1">
+      <c r="A82" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C82" s="3">
         <v>3.0</v>
-      </c>
-    </row>
-    <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="B82" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C82" s="2">
-        <v>4.0</v>
       </c>
     </row>
     <row r="83" ht="15.75" customHeight="1">
       <c r="A83" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="B83" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C83" s="2">
-        <v>4.0</v>
+        <v>96</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C83" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="84" ht="15.75" customHeight="1">
       <c r="A84" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="B84" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" s="2">
-        <v>4.0</v>
+        <v>97</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="C84" s="4">
+        <v>1.0</v>
       </c>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="3" t="s">
-        <v>94</v>
+      <c r="A85" s="1" t="s">
+        <v>98</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>67</v>
+        <v>12</v>
       </c>
       <c r="C85" s="4">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
     </row>
     <row r="86" ht="15.75" customHeight="1">
       <c r="A86" s="1" t="s">
-        <v>95</v>
-      </c>
-      <c r="B86" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C86" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C86" s="4"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="3" t="s">
-        <v>97</v>
+      <c r="A87" s="1" t="s">
+        <v>100</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C87" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C87" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="3" t="s">
-        <v>98</v>
+      <c r="A88" s="1" t="s">
+        <v>101</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C88" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="C88" s="4"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="3" t="s">
-        <v>99</v>
+      <c r="A89" s="1" t="s">
+        <v>102</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C89" s="2"/>
+        <v>28</v>
+      </c>
+      <c r="C89" s="4"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="B90" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C90" s="2"/>
+      <c r="A90" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="B90" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C90" s="3">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="91" ht="15.75" customHeight="1">
       <c r="A91" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="B91" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C91" s="2"/>
+        <v>104</v>
+      </c>
+      <c r="B91" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C91" s="3">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="92" ht="15.75" customHeight="1">
       <c r="A92" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="B92" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C92" s="2"/>
+        <v>105</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" s="4"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
       <c r="A93" s="1" t="s">
-        <v>103</v>
-      </c>
-      <c r="B93" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C93" s="2"/>
+        <v>106</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C93" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="1" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C94" s="2"/>
+        <v>9</v>
+      </c>
+      <c r="C94" s="4">
+        <v>5.0</v>
+      </c>
     </row>
     <row r="95" ht="15.75" customHeight="1">
       <c r="A95" s="1" t="s">
-        <v>106</v>
-      </c>
-      <c r="B95" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C95" s="2"/>
+        <v>108</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C95" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="B96" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C96" s="2"/>
+      <c r="A96" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="B96" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C96" s="3">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="97" ht="15.75" customHeight="1">
       <c r="A97" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="B97" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C97" s="2"/>
+        <v>110</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C97" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="B98" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C98" s="2"/>
+      <c r="A98" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="B98" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C98" s="3">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="3" t="s">
-        <v>110</v>
+      <c r="A99" s="1" t="s">
+        <v>112</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C99" s="2"/>
+        <v>7</v>
+      </c>
+      <c r="C99" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="3" t="s">
-        <v>111</v>
+      <c r="A100" s="1" t="s">
+        <v>113</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="C100" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="C100" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C101" s="2"/>
+      <c r="A101" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" s="3">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="3" t="s">
-        <v>114</v>
+      <c r="A102" s="1" t="s">
+        <v>115</v>
       </c>
       <c r="B102" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C102" s="2"/>
+        <v>16</v>
+      </c>
+      <c r="C102" s="4"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="B103" s="2" t="s">
+      <c r="A103" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C103" s="2"/>
+      <c r="B103" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C103" s="3">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="1" t="s">
+      <c r="A104" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="B104" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C104" s="2"/>
+      <c r="B104" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="C104" s="4"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
       <c r="A105" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="B105" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C105" s="2"/>
+      <c r="B105" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="4">
+        <v>1.0</v>
+      </c>
     </row>
     <row r="106" ht="15.75" customHeight="1">
       <c r="A106" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C106" s="2"/>
+        <v>119</v>
+      </c>
+      <c r="B106" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C106" s="4">
+        <v>2.0</v>
+      </c>
     </row>
     <row r="107" ht="15.75" customHeight="1">
       <c r="A107" s="1" t="s">
-        <v>119</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C107" s="2"/>
+        <v>120</v>
+      </c>
+      <c r="B107" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="C107" s="4">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="108" ht="15.75" customHeight="1">
       <c r="A108" s="1" t="s">
-        <v>120</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C108" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="B108" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C108" s="3">
+        <v>4.0</v>
+      </c>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="3" t="s">
-        <v>121</v>
+      <c r="A109" s="1" t="s">
+        <v>122</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="C109" s="2"/>
+        <v>25</v>
+      </c>
+      <c r="C109" s="3">
+        <v>3.0</v>
+      </c>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="B110" s="2" t="s">
+      <c r="A110" s="1" t="s">
         <v>123</v>
       </c>
+      <c r="B110" s="4" t="s">
+        <v>25</v>
+      </c>
       <c r="C110" s="4">
+        <v>2.0</v>
+      </c>
+    </row>
+    <row r="111" ht="15.75" customHeight="1">
+      <c r="A111" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="B111" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C111" s="4">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="112" ht="15.75" customHeight="1">
+      <c r="A112" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="B112" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C112" s="3">
+        <v>1.0</v>
+      </c>
+    </row>
+    <row r="113" ht="15.75" customHeight="1">
+      <c r="A113" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="B113" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C113" s="3">
         <v>4.0</v>
-      </c>
-    </row>
-    <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C111" s="4">
-        <v>3.0</v>
-      </c>
-    </row>
-    <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C112" s="4">
-        <v>2.0</v>
-      </c>
-    </row>
-    <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="1" t="s">
-        <v>126</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C113" s="4">
-        <v>1.0</v>
       </c>
     </row>
     <row r="114" ht="15.75" customHeight="1">
       <c r="A114" s="1" t="s">
         <v>127</v>
       </c>
-      <c r="B114" s="2" t="s">
-        <v>123</v>
+      <c r="B114" s="4" t="s">
+        <v>25</v>
       </c>
       <c r="C114" s="4">
-        <v>1.0</v>
+        <v>2.0</v>
       </c>
     </row>
     <row r="115" ht="15.75" customHeight="1">
       <c r="A115" s="1" t="s">
         <v>128</v>
       </c>
-      <c r="B115" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C115" s="4">
+      <c r="B115" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C115" s="3">
         <v>1.0</v>
       </c>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="3" t="s">
+      <c r="A116" s="1" t="s">
         <v>129</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>123</v>
+        <v>25</v>
       </c>
       <c r="C116" s="4">
         <v>1.0</v>
@@ -3040,8 +3238,8 @@
     </row>
     <row r="2" ht="15.75" customHeight="1">
       <c r="A2" s="1"/>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
     </row>
     <row r="3" ht="15.75" customHeight="1"/>
     <row r="4" ht="15.75" customHeight="1"/>
@@ -4055,7 +4253,7 @@
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="21.88"/>
-    <col customWidth="1" min="2" max="2" width="42.63"/>
+    <col customWidth="1" min="2" max="2" width="67.88"/>
     <col customWidth="1" min="3" max="6" width="12.63"/>
   </cols>
   <sheetData>
@@ -4192,7 +4390,7 @@
         <v>137</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C5" s="7"/>
       <c r="D5" s="7"/>
@@ -4224,7 +4422,7 @@
         <v>138</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C6" s="7"/>
       <c r="D6" s="7"/>
@@ -4256,7 +4454,7 @@
         <v>139</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>112</v>
+        <v>43</v>
       </c>
       <c r="C7" s="7"/>
       <c r="D7" s="7"/>
@@ -4384,7 +4582,7 @@
         <v>146</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C11" s="7"/>
       <c r="D11" s="7"/>
@@ -4608,7 +4806,7 @@
         <v>159</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
@@ -4640,7 +4838,7 @@
         <v>160</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>129</v>
+        <v>79</v>
       </c>
       <c r="C19" s="7"/>
       <c r="D19" s="7"/>
@@ -4960,7 +5158,7 @@
         <v>179</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>47</v>
+        <v>120</v>
       </c>
       <c r="C29" s="7"/>
       <c r="D29" s="7"/>
@@ -5120,7 +5318,7 @@
         <v>188</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>29</v>
+        <v>47</v>
       </c>
       <c r="C34" s="7"/>
       <c r="D34" s="7"/>
@@ -5148,8 +5346,12 @@
       <c r="Z34" s="7"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="10"/>
-      <c r="B35" s="11"/>
+      <c r="A35" s="8" t="s">
+        <v>189</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>190</v>
+      </c>
       <c r="C35" s="7"/>
       <c r="D35" s="7"/>
       <c r="E35" s="7"/>
@@ -5176,8 +5378,12 @@
       <c r="Z35" s="7"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="10"/>
-      <c r="B36" s="11"/>
+      <c r="A36" s="8" t="s">
+        <v>191</v>
+      </c>
+      <c r="B36" s="9" t="s">
+        <v>192</v>
+      </c>
       <c r="C36" s="7"/>
       <c r="D36" s="7"/>
       <c r="E36" s="7"/>
@@ -5204,8 +5410,12 @@
       <c r="Z36" s="7"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="10"/>
-      <c r="B37" s="11"/>
+      <c r="A37" s="8" t="s">
+        <v>193</v>
+      </c>
+      <c r="B37" s="9" t="s">
+        <v>194</v>
+      </c>
       <c r="C37" s="7"/>
       <c r="D37" s="7"/>
       <c r="E37" s="7"/>
@@ -5232,8 +5442,12 @@
       <c r="Z37" s="7"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="10"/>
-      <c r="B38" s="11"/>
+      <c r="A38" s="8" t="s">
+        <v>195</v>
+      </c>
+      <c r="B38" s="9" t="s">
+        <v>196</v>
+      </c>
       <c r="C38" s="7"/>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
@@ -5260,8 +5474,12 @@
       <c r="Z38" s="7"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="10"/>
-      <c r="B39" s="11"/>
+      <c r="A39" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="B39" s="9" t="s">
+        <v>198</v>
+      </c>
       <c r="C39" s="7"/>
       <c r="D39" s="7"/>
       <c r="E39" s="7"/>
@@ -5288,8 +5506,12 @@
       <c r="Z39" s="7"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="10"/>
-      <c r="B40" s="11"/>
+      <c r="A40" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>200</v>
+      </c>
       <c r="C40" s="7"/>
       <c r="D40" s="7"/>
       <c r="E40" s="7"/>
@@ -5316,8 +5538,12 @@
       <c r="Z40" s="7"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="10"/>
-      <c r="B41" s="11"/>
+      <c r="A41" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="B41" s="9" t="s">
+        <v>202</v>
+      </c>
       <c r="C41" s="7"/>
       <c r="D41" s="7"/>
       <c r="E41" s="7"/>
@@ -5344,8 +5570,12 @@
       <c r="Z41" s="7"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="10"/>
-      <c r="B42" s="11"/>
+      <c r="A42" s="8" t="s">
+        <v>203</v>
+      </c>
+      <c r="B42" s="9" t="s">
+        <v>204</v>
+      </c>
       <c r="C42" s="7"/>
       <c r="D42" s="7"/>
       <c r="E42" s="7"/>
@@ -5372,8 +5602,12 @@
       <c r="Z42" s="7"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="10"/>
-      <c r="B43" s="11"/>
+      <c r="A43" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>206</v>
+      </c>
       <c r="C43" s="7"/>
       <c r="D43" s="7"/>
       <c r="E43" s="7"/>
@@ -5400,8 +5634,12 @@
       <c r="Z43" s="7"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="10"/>
-      <c r="B44" s="11"/>
+      <c r="A44" s="8" t="s">
+        <v>207</v>
+      </c>
+      <c r="B44" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="C44" s="7"/>
       <c r="D44" s="7"/>
       <c r="E44" s="7"/>
@@ -5428,8 +5666,12 @@
       <c r="Z44" s="7"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="10"/>
-      <c r="B45" s="11"/>
+      <c r="A45" s="8" t="s">
+        <v>208</v>
+      </c>
+      <c r="B45" s="9" t="s">
+        <v>209</v>
+      </c>
       <c r="C45" s="7"/>
       <c r="D45" s="7"/>
       <c r="E45" s="7"/>
@@ -5456,8 +5698,12 @@
       <c r="Z45" s="7"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="10"/>
-      <c r="B46" s="11"/>
+      <c r="A46" s="8" t="s">
+        <v>210</v>
+      </c>
+      <c r="B46" s="9" t="s">
+        <v>211</v>
+      </c>
       <c r="C46" s="7"/>
       <c r="D46" s="7"/>
       <c r="E46" s="7"/>
@@ -5484,8 +5730,12 @@
       <c r="Z46" s="7"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="10"/>
-      <c r="B47" s="11"/>
+      <c r="A47" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="B47" s="9" t="s">
+        <v>213</v>
+      </c>
       <c r="C47" s="7"/>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
@@ -5512,8 +5762,12 @@
       <c r="Z47" s="7"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="10"/>
-      <c r="B48" s="11"/>
+      <c r="A48" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="B48" s="9" t="s">
+        <v>215</v>
+      </c>
       <c r="C48" s="7"/>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
@@ -5540,8 +5794,12 @@
       <c r="Z48" s="7"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="10"/>
-      <c r="B49" s="11"/>
+      <c r="A49" s="8" t="s">
+        <v>216</v>
+      </c>
+      <c r="B49" s="9" t="s">
+        <v>217</v>
+      </c>
       <c r="C49" s="7"/>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
@@ -5568,8 +5826,12 @@
       <c r="Z49" s="7"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="10"/>
-      <c r="B50" s="11"/>
+      <c r="A50" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="B50" s="9" t="s">
+        <v>219</v>
+      </c>
       <c r="C50" s="7"/>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
@@ -5596,8 +5858,12 @@
       <c r="Z50" s="7"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="10"/>
-      <c r="B51" s="11"/>
+      <c r="A51" s="8" t="s">
+        <v>220</v>
+      </c>
+      <c r="B51" s="9" t="s">
+        <v>221</v>
+      </c>
       <c r="C51" s="7"/>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
@@ -5624,8 +5890,12 @@
       <c r="Z51" s="7"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="10"/>
-      <c r="B52" s="11"/>
+      <c r="A52" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="B52" s="9" t="s">
+        <v>223</v>
+      </c>
       <c r="C52" s="7"/>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
@@ -5652,8 +5922,12 @@
       <c r="Z52" s="7"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="10"/>
-      <c r="B53" s="11"/>
+      <c r="A53" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B53" s="9" t="s">
+        <v>225</v>
+      </c>
       <c r="C53" s="7"/>
       <c r="D53" s="7"/>
       <c r="E53" s="7"/>
@@ -5680,8 +5954,12 @@
       <c r="Z53" s="7"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="10"/>
-      <c r="B54" s="11"/>
+      <c r="A54" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="B54" s="9" t="s">
+        <v>221</v>
+      </c>
       <c r="C54" s="7"/>
       <c r="D54" s="7"/>
       <c r="E54" s="7"/>
@@ -5708,8 +5986,12 @@
       <c r="Z54" s="7"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="10"/>
-      <c r="B55" s="11"/>
+      <c r="A55" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="B55" s="9" t="s">
+        <v>228</v>
+      </c>
       <c r="C55" s="7"/>
       <c r="D55" s="7"/>
       <c r="E55" s="7"/>
@@ -5736,8 +6018,12 @@
       <c r="Z55" s="7"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="10"/>
-      <c r="B56" s="11"/>
+      <c r="A56" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="B56" s="9" t="s">
+        <v>43</v>
+      </c>
       <c r="C56" s="7"/>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -5764,8 +6050,12 @@
       <c r="Z56" s="7"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="10"/>
-      <c r="B57" s="11"/>
+      <c r="A57" s="8" t="s">
+        <v>230</v>
+      </c>
+      <c r="B57" s="9" t="s">
+        <v>231</v>
+      </c>
       <c r="C57" s="7"/>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -5792,8 +6082,12 @@
       <c r="Z57" s="7"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="10"/>
-      <c r="B58" s="11"/>
+      <c r="A58" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="B58" s="9" t="s">
+        <v>233</v>
+      </c>
       <c r="C58" s="7"/>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -5820,8 +6114,12 @@
       <c r="Z58" s="7"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="10"/>
-      <c r="B59" s="11"/>
+      <c r="A59" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="B59" s="9" t="s">
+        <v>235</v>
+      </c>
       <c r="C59" s="7"/>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -5848,8 +6146,12 @@
       <c r="Z59" s="7"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="10"/>
-      <c r="B60" s="11"/>
+      <c r="A60" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B60" s="9" t="s">
+        <v>237</v>
+      </c>
       <c r="C60" s="7"/>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -5876,8 +6178,12 @@
       <c r="Z60" s="7"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="10"/>
-      <c r="B61" s="11"/>
+      <c r="A61" s="8" t="s">
+        <v>238</v>
+      </c>
+      <c r="B61" s="9" t="s">
+        <v>239</v>
+      </c>
       <c r="C61" s="7"/>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -5904,8 +6210,12 @@
       <c r="Z61" s="7"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="10"/>
-      <c r="B62" s="11"/>
+      <c r="A62" s="8" t="s">
+        <v>240</v>
+      </c>
+      <c r="B62" s="9" t="s">
+        <v>241</v>
+      </c>
       <c r="C62" s="7"/>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -5932,8 +6242,12 @@
       <c r="Z62" s="7"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="10"/>
-      <c r="B63" s="11"/>
+      <c r="A63" s="8" t="s">
+        <v>242</v>
+      </c>
+      <c r="B63" s="9" t="s">
+        <v>243</v>
+      </c>
       <c r="C63" s="7"/>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
@@ -5960,8 +6274,12 @@
       <c r="Z63" s="7"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="10"/>
-      <c r="B64" s="11"/>
+      <c r="A64" s="8" t="s">
+        <v>244</v>
+      </c>
+      <c r="B64" s="9" t="s">
+        <v>202</v>
+      </c>
       <c r="C64" s="7"/>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
@@ -5988,8 +6306,12 @@
       <c r="Z64" s="7"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="10"/>
-      <c r="B65" s="11"/>
+      <c r="A65" s="8" t="s">
+        <v>245</v>
+      </c>
+      <c r="B65" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="C65" s="7"/>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
@@ -6016,8 +6338,12 @@
       <c r="Z65" s="7"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="10"/>
-      <c r="B66" s="11"/>
+      <c r="A66" s="8" t="s">
+        <v>246</v>
+      </c>
+      <c r="B66" s="9" t="s">
+        <v>247</v>
+      </c>
       <c r="C66" s="7"/>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
@@ -6044,8 +6370,12 @@
       <c r="Z66" s="7"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="10"/>
-      <c r="B67" s="11"/>
+      <c r="A67" s="8" t="s">
+        <v>248</v>
+      </c>
+      <c r="B67" s="9" t="s">
+        <v>249</v>
+      </c>
       <c r="C67" s="7"/>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
@@ -6072,8 +6402,12 @@
       <c r="Z67" s="7"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="10"/>
-      <c r="B68" s="11"/>
+      <c r="A68" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="B68" s="9" t="s">
+        <v>47</v>
+      </c>
       <c r="C68" s="7"/>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
@@ -6100,8 +6434,12 @@
       <c r="Z68" s="7"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="10"/>
-      <c r="B69" s="11"/>
+      <c r="A69" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="B69" s="9" t="s">
+        <v>252</v>
+      </c>
       <c r="C69" s="7"/>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
@@ -6128,8 +6466,12 @@
       <c r="Z69" s="7"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="10"/>
-      <c r="B70" s="11"/>
+      <c r="A70" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="B70" s="9" t="s">
+        <v>254</v>
+      </c>
       <c r="C70" s="7"/>
       <c r="D70" s="7"/>
       <c r="E70" s="7"/>
@@ -31691,10 +32033,38 @@
       <c r="Y982" s="7"/>
       <c r="Z982" s="7"/>
     </row>
+    <row r="983" ht="15.75" customHeight="1">
+      <c r="A983" s="10"/>
+      <c r="B983" s="11"/>
+      <c r="C983" s="7"/>
+      <c r="D983" s="7"/>
+      <c r="E983" s="7"/>
+      <c r="F983" s="7"/>
+      <c r="G983" s="7"/>
+      <c r="H983" s="7"/>
+      <c r="I983" s="7"/>
+      <c r="J983" s="7"/>
+      <c r="K983" s="7"/>
+      <c r="L983" s="7"/>
+      <c r="M983" s="7"/>
+      <c r="N983" s="7"/>
+      <c r="O983" s="7"/>
+      <c r="P983" s="7"/>
+      <c r="Q983" s="7"/>
+      <c r="R983" s="7"/>
+      <c r="S983" s="7"/>
+      <c r="T983" s="7"/>
+      <c r="U983" s="7"/>
+      <c r="V983" s="7"/>
+      <c r="W983" s="7"/>
+      <c r="X983" s="7"/>
+      <c r="Y983" s="7"/>
+      <c r="Z983" s="7"/>
+    </row>
   </sheetData>
-  <autoFilter ref="$A$1:$B$34">
-    <sortState ref="A1:B34">
-      <sortCondition ref="A1:A34"/>
+  <autoFilter ref="$A$1:$B$70">
+    <sortState ref="A1:B70">
+      <sortCondition ref="A1:A70"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>
